--- a/datos-referencia/facturas_ota_demo.xlsx
+++ b/datos-referencia/facturas_ota_demo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,199 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>discrepancia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BK-2026-0501</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CORRECTA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EXP-2026-0501</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2232</v>
+      </c>
+      <c r="F3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CORRECTA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HotelBeds</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HB-2026-0501</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DISCREPANCIA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Comisión 15% vs pactado 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BK-2026-0601</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4815</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CORRECTA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hotusa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HT-2026-0601</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5600</v>
+      </c>
+      <c r="E6" t="n">
+        <v>952</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DISCREPANCIA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Comisión 17% vs pactado 14%</t>
         </is>
       </c>
     </row>
